--- a/PFP-C/Input data and Generated Schedule/28.xlsx
+++ b/PFP-C/Input data and Generated Schedule/28.xlsx
@@ -31608,7 +31608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31633,7 +31633,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>objective all vehicle travel individually</t>
+          <t>objective_all_vehicle_travel_individually</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -31643,7 +31643,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>objective LLA</t>
+          <t>objective_LLA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -31653,11 +31653,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>objective lb</t>
+          <t>objective_lb</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>45.20800000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -42718,7 +42838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42754,25 +42874,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Saving_time_(minute)</t>
+          <t>Saving_time(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -42805,18 +42920,15 @@
         <v>4.642857142857147</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>294.3423423423422</v>
       </c>
       <c r="I2" t="n">
-        <v>294.3423423423422</v>
+        <v>2.342342342342344</v>
       </c>
       <c r="J2" t="n">
-        <v>2.342342342342344</v>
-      </c>
-      <c r="K2" t="n">
         <v>0.795788442703233</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42849,18 +42961,15 @@
         <v>4.28070175438596</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>242.4286786786786</v>
       </c>
       <c r="I3" t="n">
-        <v>242.4286786786786</v>
+        <v>1.83183183183183</v>
       </c>
       <c r="J3" t="n">
-        <v>1.83183183183183</v>
-      </c>
-      <c r="K3" t="n">
         <v>0.7556168031834998</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42893,18 +43002,15 @@
         <v>7.305122494432077</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>398.4617117117117</v>
       </c>
       <c r="I4" t="n">
-        <v>398.4617117117117</v>
+        <v>4.924924924924929</v>
       </c>
       <c r="J4" t="n">
-        <v>4.924924924924929</v>
-      </c>
-      <c r="K4" t="n">
         <v>1.235984482365555</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42937,18 +43043,15 @@
         <v>2.838874680306899</v>
       </c>
       <c r="H5" t="n">
-        <v>-25.31945374101446</v>
+        <v>329.7364864864865</v>
       </c>
       <c r="I5" t="n">
-        <v>329.7364864864865</v>
+        <v>1.666666666666663</v>
       </c>
       <c r="J5" t="n">
-        <v>1.666666666666663</v>
-      </c>
-      <c r="K5" t="n">
         <v>0.5054541232078567</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -42981,18 +43084,15 @@
         <v>5.374449339207043</v>
       </c>
       <c r="H6" t="n">
-        <v>-28.07747106674651</v>
+        <v>187.216966966967</v>
       </c>
       <c r="I6" t="n">
-        <v>187.216966966967</v>
+        <v>1.83183183183183</v>
       </c>
       <c r="J6" t="n">
-        <v>1.83183183183183</v>
-      </c>
-      <c r="K6" t="n">
         <v>0.9784539625380442</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43025,18 +43125,15 @@
         <v>3.709090909090904</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>231.9256756756756</v>
       </c>
       <c r="I7" t="n">
-        <v>231.9256756756756</v>
+        <v>1.531531531531529</v>
       </c>
       <c r="J7" t="n">
-        <v>1.531531531531529</v>
-      </c>
-      <c r="K7" t="n">
         <v>0.6603544549647967</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43069,18 +43166,15 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>239.1328828828828</v>
       </c>
       <c r="I8" t="n">
-        <v>239.1328828828828</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43113,18 +43207,15 @@
         <v>4.647201946472015</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>374.7665165165165</v>
       </c>
       <c r="I9" t="n">
-        <v>374.7665165165165</v>
+        <v>2.867867867867865</v>
       </c>
       <c r="J9" t="n">
-        <v>2.867867867867865</v>
-      </c>
-      <c r="K9" t="n">
         <v>0.7652412212608845</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43157,18 +43248,15 @@
         <v>6.822916666666644</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>329.4414414414414</v>
       </c>
       <c r="I10" t="n">
-        <v>329.4414414414414</v>
+        <v>3.933933933933921</v>
       </c>
       <c r="J10" t="n">
-        <v>3.933933933933921</v>
-      </c>
-      <c r="K10" t="n">
         <v>1.194122365638441</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43201,18 +43289,15 @@
         <v>8.671874999999982</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>338.4504504504505</v>
       </c>
       <c r="I11" t="n">
-        <v>338.4504504504505</v>
+        <v>4.999999999999989</v>
       </c>
       <c r="J11" t="n">
-        <v>4.999999999999989</v>
-      </c>
-      <c r="K11" t="n">
         <v>1.477321124361155</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43245,18 +43330,15 @@
         <v>1.528662420382167</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>276.3408408408408</v>
       </c>
       <c r="I12" t="n">
-        <v>276.3408408408408</v>
+        <v>0.7207207207207212</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7207207207207212</v>
-      </c>
-      <c r="K12" t="n">
         <v>0.2608086153779282</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43289,18 +43371,15 @@
         <v>7.059999999999995</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>433.8588588588589</v>
       </c>
       <c r="I13" t="n">
-        <v>433.8588588588589</v>
+        <v>5.300300300300296</v>
       </c>
       <c r="J13" t="n">
-        <v>5.300300300300296</v>
-      </c>
-      <c r="K13" t="n">
         <v>1.221664647862951</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43333,18 +43412,15 @@
         <v>9.07801418439716</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>385.5683183183182</v>
       </c>
       <c r="I14" t="n">
-        <v>385.5683183183182</v>
+        <v>5.765765765765764</v>
       </c>
       <c r="J14" t="n">
-        <v>5.765765765765764</v>
-      </c>
-      <c r="K14" t="n">
         <v>1.495394069438468</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43377,18 +43453,15 @@
         <v>9.155844155844136</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>407.1606606606608</v>
       </c>
       <c r="I15" t="n">
-        <v>407.1606606606608</v>
+        <v>6.351351351351338</v>
       </c>
       <c r="J15" t="n">
-        <v>6.351351351351338</v>
-      </c>
-      <c r="K15" t="n">
         <v>1.559912821893354</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43421,18 +43494,15 @@
         <v>5.911458333333319</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>339.0510510510509</v>
       </c>
       <c r="I16" t="n">
-        <v>339.0510510510509</v>
+        <v>3.4084084084084</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4084084084084</v>
-      </c>
-      <c r="K16" t="n">
         <v>1.005278820945226</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43465,18 +43535,15 @@
         <v>4.851190476190483</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>285.0330330330331</v>
       </c>
       <c r="I17" t="n">
-        <v>285.0330330330331</v>
+        <v>2.447447447447451</v>
       </c>
       <c r="J17" t="n">
-        <v>2.447447447447451</v>
-      </c>
-      <c r="K17" t="n">
         <v>0.8586539677188261</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43509,18 +43576,15 @@
         <v>5.446428571428566</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>301.5495495495496</v>
       </c>
       <c r="I18" t="n">
-        <v>301.5495495495496</v>
+        <v>2.747747747747745</v>
       </c>
       <c r="J18" t="n">
-        <v>2.747747747747745</v>
-      </c>
-      <c r="K18" t="n">
         <v>0.9112093690248555</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43553,18 +43617,15 @@
         <v>3.279569892473127</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>318.039039039039</v>
       </c>
       <c r="I19" t="n">
-        <v>318.039039039039</v>
+        <v>1.831831831831837</v>
       </c>
       <c r="J19" t="n">
-        <v>1.831831831831837</v>
-      </c>
-      <c r="K19" t="n">
         <v>0.5759770364565152</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43597,18 +43658,15 @@
         <v>8.085106382978724</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>371.1539039039039</v>
       </c>
       <c r="I20" t="n">
-        <v>371.1539039039039</v>
+        <v>5.135135135135136</v>
       </c>
       <c r="J20" t="n">
-        <v>5.135135135135136</v>
-      </c>
-      <c r="K20" t="n">
         <v>1.383559510252298</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43641,18 +43699,15 @@
         <v>1.255411255411252</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>411.0645645645645</v>
       </c>
       <c r="I21" t="n">
-        <v>411.0645645645645</v>
+        <v>0.8708708708708682</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8708708708708682</v>
-      </c>
-      <c r="K21" t="n">
         <v>0.2118574418579161</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43685,18 +43740,15 @@
         <v>7.800511508951399</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.217499056888698</v>
+        <v>334.240990990991</v>
       </c>
       <c r="I22" t="n">
-        <v>334.240990990991</v>
+        <v>4.579579579579575</v>
       </c>
       <c r="J22" t="n">
-        <v>4.579579579579575</v>
-      </c>
-      <c r="K22" t="n">
         <v>1.370143011484492</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43729,18 +43781,15 @@
         <v>7.41999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>450.0750750750751</v>
       </c>
       <c r="I23" t="n">
-        <v>450.0750750750751</v>
+        <v>5.570570570570563</v>
       </c>
       <c r="J23" t="n">
-        <v>5.570570570570563</v>
-      </c>
-      <c r="K23" t="n">
         <v>1.237698081734777</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43773,18 +43822,15 @@
         <v>3.28605200945627</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>355.237987987988</v>
       </c>
       <c r="I24" t="n">
-        <v>355.237987987988</v>
+        <v>2.08708708708709</v>
       </c>
       <c r="J24" t="n">
-        <v>2.08708708708709</v>
-      </c>
-      <c r="K24" t="n">
         <v>0.58751799009673</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43817,18 +43863,15 @@
         <v>6.301703163017039</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>366.0578078078078</v>
       </c>
       <c r="I25" t="n">
-        <v>366.0578078078078</v>
+        <v>3.888888888888894</v>
       </c>
       <c r="J25" t="n">
-        <v>3.888888888888894</v>
-      </c>
-      <c r="K25" t="n">
         <v>1.062370151910729</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43861,18 +43904,15 @@
         <v>8.58880778588807</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>365.7575075075074</v>
       </c>
       <c r="I26" t="n">
-        <v>365.7575075075074</v>
+        <v>5.300300300300296</v>
       </c>
       <c r="J26" t="n">
-        <v>5.300300300300296</v>
-      </c>
-      <c r="K26" t="n">
         <v>1.44912959857468</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43889,7 +43929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43915,20 +43955,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time_(minute)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving_time(%)</t>
         </is>
@@ -43961,9 +43996,6 @@
       <c r="H2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -43984,15 +44016,12 @@
         <v>5.493674002926815</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.264576954585987</v>
+        <v>334.6436936936936</v>
       </c>
       <c r="G3" t="n">
-        <v>334.6436936936936</v>
+        <v>3.277477477477475</v>
       </c>
       <c r="H3" t="n">
-        <v>3.277477477477475</v>
-      </c>
-      <c r="I3" t="n">
         <v>0.9423804845941285</v>
       </c>
     </row>
@@ -44015,15 +44044,12 @@
         <v>2.559547029572462</v>
       </c>
       <c r="F4" t="n">
-        <v>7.392461531427893</v>
+        <v>66.17753914874655</v>
       </c>
       <c r="G4" t="n">
-        <v>66.17753914874655</v>
+        <v>1.815945488823586</v>
       </c>
       <c r="H4" t="n">
-        <v>1.815945488823586</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.4308338716730831</v>
       </c>
     </row>
@@ -44046,15 +44072,12 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-28.07747106674651</v>
+        <v>187.216966966967</v>
       </c>
       <c r="G5" t="n">
-        <v>187.216966966967</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44077,15 +44100,12 @@
         <v>3.709090909090904</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>294.3423423423422</v>
       </c>
       <c r="G6" t="n">
-        <v>294.3423423423422</v>
+        <v>1.83183183183183</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83183183183183</v>
-      </c>
-      <c r="I6" t="n">
         <v>0.6603544549647967</v>
       </c>
     </row>
@@ -44108,15 +44128,12 @@
         <v>5.446428571428566</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>338.4504504504505</v>
       </c>
       <c r="G7" t="n">
-        <v>338.4504504504505</v>
+        <v>2.867867867867865</v>
       </c>
       <c r="H7" t="n">
-        <v>2.867867867867865</v>
-      </c>
-      <c r="I7" t="n">
         <v>0.9784539625380442</v>
       </c>
     </row>
@@ -44139,15 +44156,12 @@
         <v>7.41999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>374.7665165165165</v>
       </c>
       <c r="G8" t="n">
-        <v>374.7665165165165</v>
+        <v>4.999999999999989</v>
       </c>
       <c r="H8" t="n">
-        <v>4.999999999999989</v>
-      </c>
-      <c r="I8" t="n">
         <v>1.237698081734777</v>
       </c>
     </row>
@@ -44170,15 +44184,12 @@
         <v>9.155844155844136</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>450.0750750750751</v>
       </c>
       <c r="G9" t="n">
-        <v>450.0750750750751</v>
+        <v>6.351351351351338</v>
       </c>
       <c r="H9" t="n">
-        <v>6.351351351351338</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.559912821893354</v>
       </c>
     </row>
